--- a/instance/uploads/warehouse.xlsx
+++ b/instance/uploads/warehouse.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/poverinov/Documents/GitHub/QR/project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4283E35-027C-A945-839D-BA717CA5B33E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D31E230-D82B-1741-886E-F45DF34549D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="21800" windowHeight="12980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
